--- a/order_forms/032_hamburger_order_form--order_forms.xlsx
+++ b/order_forms/032_hamburger_order_form--order_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -665,8 +665,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
-    <col width="36" customWidth="1" min="2" max="2"/>
-    <col width="36" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -694,12 +694,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'john_doe'}</t>
+          <t>john_doe</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'John Doe'}</t>
+          <t>John Doe</t>
         </is>
       </c>
     </row>
@@ -711,12 +711,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'jane_doe'}</t>
+          <t>jane_doe</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Jane Doe'}</t>
+          <t>Jane Doe</t>
         </is>
       </c>
     </row>
@@ -728,12 +728,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'john_smith'}</t>
+          <t>john_smith</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'John Smith'}</t>
+          <t>John Smith</t>
         </is>
       </c>
     </row>
@@ -745,12 +745,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'beef_patty'}</t>
+          <t>beef_patty</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Beef patty'}</t>
+          <t>Beef patty</t>
         </is>
       </c>
     </row>
@@ -762,12 +762,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'veggie_patty'}</t>
+          <t>veggie_patty</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Veggie patty'}</t>
+          <t>Veggie patty</t>
         </is>
       </c>
     </row>
@@ -779,12 +779,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'chicken_patty'}</t>
+          <t>chicken_patty</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'Chicken patty'}</t>
+          <t>Chicken patty</t>
         </is>
       </c>
     </row>
@@ -796,12 +796,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_4,_'name':_'none'}</t>
+          <t>none</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 4, 'name': 'None'}</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -813,12 +813,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'small'}</t>
+          <t>small</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Small'}</t>
+          <t>Small</t>
         </is>
       </c>
     </row>
@@ -830,12 +830,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'medium'}</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Medium'}</t>
+          <t>Medium</t>
         </is>
       </c>
     </row>
@@ -847,12 +847,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'large'}</t>
+          <t>large</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'Large'}</t>
+          <t>Large</t>
         </is>
       </c>
     </row>
@@ -864,12 +864,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'cash'}</t>
+          <t>cash</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Cash'}</t>
+          <t>Cash</t>
         </is>
       </c>
     </row>
@@ -881,12 +881,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'credit_card'}</t>
+          <t>credit_card</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Credit Card'}</t>
+          <t>Credit Card</t>
         </is>
       </c>
     </row>
@@ -898,12 +898,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'bank_transfer'}</t>
+          <t>bank_transfer</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'Bank Transfer'}</t>
+          <t>Bank Transfer</t>
         </is>
       </c>
     </row>
